--- a/eval/question_bank.xlsx
+++ b/eval/question_bank.xlsx
@@ -1253,37 +1253,37 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>함정-무근거</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>건축학전공은 졸업학점이 몇이야?</t>
+          <t>학사경고 받으면 다음 학기에 수강신청할 수 있는 학점이 줄어들어?</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>How many credits does the Architecture major require for graduation?</t>
+          <t>If I get an academic warning, will my credit limit for next semester be reduced?</t>
         </is>
       </c>
       <c r="F13" s="11" t="inlineStr">
         <is>
-          <t>158학점 (2016학번부터). 그 전 학번은 160·164</t>
+          <t>(자료에 없음. 학칙에는 학사경고 기준만 있음 → 학과 교학팀·교무팀 안내가 정답)</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>아주대학교 학칙, 학사지원 졸업 안내</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>제50조(학사과정의 졸업요건) ① · https://rules.ajou.ac.kr/IRS/rule/detail/594</t>
+          <t>(학칙 제47조는 학사경고 기준만 규정)</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>158이면 정답. 학번 차이를 언급해도 정답. 160·164를 단정하면 오답</t>
+          <t>수강 학점이 줄어든다거나 몇 학점으로 제한된다고 지어내면 오답. 학사경고 기준만 안내하고 수강 제한은 확인하라고 하면 정답</t>
         </is>
       </c>
       <c r="J13" s="10" t="n"/>
@@ -1291,7 +1291,7 @@
       <c r="L13" s="11" t="n"/>
       <c r="M13" s="11" t="inlineStr">
         <is>
-          <t>구간 A</t>
+          <t>구간 C · 10/27 재점검: 기존 '건축학전공 졸업학점'(9·18번과 겹침)을 새 함정으로 교체</t>
         </is>
       </c>
     </row>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>학사지원 졸업 안내</t>
+          <t>아주대학교 졸업 안내</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>연도별 졸업요건 · https://www.ajou.ac.kr/kr/bachelor/regs-graduation.do</t>
+          <t>졸업요건 · https://www.ajou.ac.kr/kr/bachelor/regs-graduation.do</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
@@ -1715,7 +1715,7 @@
       <c r="L21" s="11" t="n"/>
       <c r="M21" s="11" t="inlineStr">
         <is>
-          <t>구간 A · 근거 페이지가 DB에 들어오기 전에는 오답 예상 — RAG 전후 비교 사례</t>
+          <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>대학원 규정을 학부에 적용하거나 상한을 지어내면 오답</t>
+          <t>대학원 규정(F 과목만 재수강)이나 학위취득유예생 재수강 규칙을 일반 학부 재수강 규칙으로 쓰거나, 상한을 지어내면 오답</t>
         </is>
       </c>
       <c r="J25" s="10" t="n"/>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>함정-무근거</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
@@ -1957,22 +1957,22 @@
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>(학부 수강신청 학점은 학사운영규칙 소관, 자료에 없음 → 안내가 정답)</t>
+          <t>학번·학과·성적에 따라 다름: 2004학번 이후 19학점(누계평점 3.75 이상 22학점), 소프트웨어학과·국방디지털융합학과는 21학점(3.75 이상 24학점), 2003학번까지 21학점(24학점)</t>
         </is>
       </c>
       <c r="G26" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아주대학교 수강신청 안내</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
         <is>
-          <t>(학칙 제46조①③)</t>
+          <t>수강신청학점 · https://www.ajou.ac.kr/kr/bachelor/enrolment.do</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>대학원의 12학점을 학부로 말하면 오답</t>
+          <t>학번·학과·평점에 따라 다르다는 점과 맞는 기준을 말하면 정답. 대학원 12학점이나 다른 값을 단정하면 오답</t>
         </is>
       </c>
       <c r="J26" s="10" t="n"/>
@@ -1980,7 +1980,7 @@
       <c r="L26" s="11" t="n"/>
       <c r="M26" s="11" t="inlineStr">
         <is>
-          <t>구간 C</t>
+          <t>구간 B · 10/27 재점검: 수강신청 안내 페이지 추가로 근거 생김 (함정 → B)</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>함정-무근거</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
@@ -2010,22 +2010,22 @@
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>(세부 기준은 학사운영규칙 소관, 자료에 없음 → 안내가 정답)</t>
+          <t>학번에 따라 다름: 2004~2013학번은 누계평점 2.50 이상(학기당 평균 14학점 이수), 2014~2024학번은 1학년 권장교육과정 이수가 원칙, 2025학번 이후는 전공과목 이수 요건. 최근 학번은 평점 기준이 없음</t>
         </is>
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아주대학교 전과 안내</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>(학칙 제31조③)</t>
+          <t>신청 자격 · https://www.ajou.ac.kr/kr/bachelor/regs-change.do</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>기준 평점을 지어내면 오답</t>
+          <t>학번별로 다르다는 점을 말하면 정답. 모든 학생에게 '평점 2.5 이상'이라고 단정하면 오답</t>
         </is>
       </c>
       <c r="J27" s="10" t="n"/>
@@ -2033,7 +2033,7 @@
       <c r="L27" s="11" t="n"/>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>구간 C · 학사지원 전과 페이지가 DB에 들어오면 정답이 생길 수 있음</t>
+          <t>구간 B · 10/27 재점검: 전과 안내 페이지 추가로 근거 생김 (함정 → B)</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2757,7 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>학사지원 휴/복학 안내</t>
+          <t>아주대학교 휴/복학 안내</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
@@ -2775,7 +2775,7 @@
       <c r="L41" s="11" t="n"/>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>구간 A · 근거 페이지가 DB에 들어오기 전에는 오답 예상</t>
+          <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>학사지원 휴/복학 안내</t>
+          <t>아주대학교 휴/복학 안내</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
@@ -2828,7 +2828,7 @@
       <c r="L42" s="11" t="n"/>
       <c r="M42" s="11" t="inlineStr">
         <is>
-          <t>구간 A · 근거 페이지가 DB에 들어오기 전에는 오답 예상</t>
+          <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
         </is>
       </c>
     </row>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>학사지원 휴/복학 안내</t>
+          <t>아주대학교 휴/복학 안내</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
@@ -2881,7 +2881,7 @@
       <c r="L43" s="11" t="n"/>
       <c r="M43" s="11" t="inlineStr">
         <is>
-          <t>구간 A · 근거 페이지가 DB에 들어오기 전에는 오답 예상</t>
+          <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>학사지원 휴/복학 안내</t>
+          <t>아주대학교 휴/복학 안내</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
@@ -2934,7 +2934,7 @@
       <c r="L44" s="11" t="n"/>
       <c r="M44" s="11" t="inlineStr">
         <is>
-          <t>구간 A · 근거 페이지가 DB에 들어오기 전에는 오답 예상</t>
+          <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>학사지원 휴/복학 안내</t>
+          <t>아주대학교 휴/복학 안내</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
@@ -2987,7 +2987,7 @@
       <c r="L45" s="11" t="n"/>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>구간 A · 근거 페이지가 DB에 들어오기 전에는 오답 예상</t>
+          <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>학부 절차를 맞게 말하면 정답</t>
+          <t>학부 절차(보증인 연서·학과장 확인 → 자퇴원서 → 총장 허가)나 학사서비스 자퇴신청 메뉴를 맞게 안내하면 정답</t>
         </is>
       </c>
       <c r="J46" s="10" t="n"/>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>함정-무근거</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -3176,22 +3176,22 @@
       </c>
       <c r="F49" s="11" t="inlineStr">
         <is>
-          <t>(자료에 없음 → 안내가 정답)</t>
+          <t>포털(AIMS2) → 주요서비스 → 증명서발급에서 인터넷 즉시 발급(24시간), 또는 종합지원센터(신학생회관 116호) 앞 무인증명발급기</t>
         </is>
       </c>
       <c r="G49" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아주대학교 증명서 발급 안내</t>
         </is>
       </c>
       <c r="H49" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>인터넷증명서 즉시 발급, 무인증명서 발급기 · https://www.ajou.ac.kr/kr/life/paper01.do</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>발급 방법을 지어내면 오답</t>
+          <t>인터넷 발급이나 무인발급기 중 하나 이상 맞게 안내하면 정답</t>
         </is>
       </c>
       <c r="J49" s="10" t="n"/>
@@ -3199,7 +3199,7 @@
       <c r="L49" s="11" t="n"/>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>구간 C</t>
+          <t>구간 A · 10/27 재점검: 증명서 발급 안내 페이지 추가로 근거 생김 (함정 → A)</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>함정-무근거</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -3282,22 +3282,22 @@
       </c>
       <c r="F51" s="11" t="inlineStr">
         <is>
-          <t>(학사일정 7건에 없음 → 안내가 정답)</t>
+          <t>2학기 수강 정정은 9월 초 (정확한 날짜는 매 학기 공지)</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아주대학교 수강신청 안내</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>수강신청 일정 · https://www.ajou.ac.kr/kr/bachelor/enrolment.do</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>날짜를 지어내면 오답</t>
+          <t>9월 초를 말하면 정답. 구체 날짜를 지어내면 오답</t>
         </is>
       </c>
       <c r="J51" s="10" t="n"/>
@@ -3305,7 +3305,7 @@
       <c r="L51" s="11" t="n"/>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>구간 C · 학사일정 전체가 수집되면 정답이 생길 수 있음</t>
+          <t>구간 A · 10/27 재점검: 수강신청 안내 페이지 추가로 근거 생김 (함정 → A)</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>금액을 지어내면 오답</t>
+          <t>금액을 지어내거나 유학생 학비(₩4,916,000)를 국내생 등록금처럼 말하면 오답. 포털 고지서 확인이나 재무회계팀 안내면 정답</t>
         </is>
       </c>
       <c r="J52" s="10" t="n"/>
@@ -3585,37 +3585,37 @@
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>함정-무근거</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>교류학생이 뭐야?</t>
+          <t>외국인 학생 입국할 때 공항 픽업 서비스 있어?</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>What is an exchange student?</t>
+          <t>Is there an airport pickup service for international students when they arrive?</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>외국 대학·기관과의 협약에 따라 본교에서 공부하는 외국인 학생</t>
+          <t>(자료에 없음 → 국제협력처 유학생입학팀 안내가 정답)</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>외국인학생 지원 및 관리에 관한 규칙</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>제2조(용어의 정의) 3호 · https://rules.ajou.ac.kr/IRS/rule/detail/293</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>"협약에 따라 수학"이 들어가면 정답</t>
+          <t>있다/없다를 지어내면 오답. 유학생입학팀 문의 안내면 정답</t>
         </is>
       </c>
       <c r="J57" s="10" t="n"/>
@@ -3623,7 +3623,7 @@
       <c r="L57" s="11" t="n"/>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>구간 A</t>
+          <t>구간 C · 10/27 재점검: 기존 '교류학생이 뭐야?'(용어 정의)를 새 함정으로 교체</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>대학일자리플러스센터가 들어가면 정답</t>
+          <t>대학일자리플러스센터나 유학생입학팀 취업특강을 안내하면 정답</t>
         </is>
       </c>
       <c r="J63" s="10" t="n"/>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G70" s="11" t="inlineStr">
         <is>
-          <t>학사지원 졸업 안내</t>
+          <t>아주대학교 졸업 안내</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
@@ -4312,7 +4312,7 @@
       <c r="L70" s="11" t="n"/>
       <c r="M70" s="11" t="inlineStr">
         <is>
-          <t>구간 A · 근거 페이지가 DB에 들어오기 전에는 오답 예상</t>
+          <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>함정-무근거</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
@@ -4501,22 +4501,22 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>(체류관리 세부 기준은 자료에 없음 → 국제협력처 유학생입학팀 안내가 정답)</t>
+          <t>체류기한 만료 전에 관할 출입국관리사무소에서 연장. 서류: 여권·외국인등록증, 체류기간연장신청서, 학비납입증명서, 재학증명서(출석률 표시), 거주확인증 또는 임차계약서, 수수료 60,000원</t>
         </is>
       </c>
       <c r="G74" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아주대학교 비자·체류 안내</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>(외국인학생 규칙 제5조③: 별도 기준)</t>
+          <t>체류기간 연장 · https://www.ajou.ac.kr/iadmissions/life/visa.do</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>절차·서류를 지어내면 오답. 담당 부서 안내면 정답</t>
+          <t>만료 전 출입국관리사무소 신청과 주요 서류를 말하면 정답. 절차·비용을 지어내면 오답</t>
         </is>
       </c>
       <c r="J74" s="10" t="n"/>
@@ -4524,7 +4524,7 @@
       <c r="L74" s="11" t="n"/>
       <c r="M74" s="11" t="inlineStr">
         <is>
-          <t>구간 C</t>
+          <t>구간 A · 10/27 재점검: 비자·체류 안내 페이지 추가로 근거 생김 (함정 → A)</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>시간을 지어내면 오답</t>
+          <t>시간을 지어내면 오답. 시간제취업 허가 절차(유학생 담당자 확인 → 출입국 신고) 안내는 정답</t>
         </is>
       </c>
       <c r="J75" s="10" t="n"/>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>함정-무근거</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
@@ -4607,22 +4607,22 @@
       </c>
       <c r="F76" s="11" t="inlineStr">
         <is>
-          <t>(자료에 없음 → 생활관 안내가 정답)</t>
+          <t>학기당 ₩747,000~₩1,440,000 (유학생 학비·생활비 안내 기준)</t>
         </is>
       </c>
       <c r="G76" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아주대학교 유학생 학비·생활비 안내</t>
         </is>
       </c>
       <c r="H76" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>기숙사비 · https://www.ajou.ac.kr/iadmissions/undergraduate/tuition.do</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>금액을 지어내면 오답</t>
+          <t>금액 범위가 맞으면 정답</t>
         </is>
       </c>
       <c r="J76" s="10" t="n"/>
@@ -4630,7 +4630,7 @@
       <c r="L76" s="11" t="n"/>
       <c r="M76" s="11" t="inlineStr">
         <is>
-          <t>구간 C</t>
+          <t>구간 A · 10/27 재점검: 유학생 학비·생활비 페이지 추가로 근거 생김 (함정 → A)</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>함정-무근거</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -5826,22 +5826,22 @@
       </c>
       <c r="F99" s="11" t="inlineStr">
         <is>
-          <t>(자료에 없음 → 기숙사 관련 부서 안내가 정답)</t>
+          <t>세탁실은 각 관과 식당동 지하 1층에 있음</t>
         </is>
       </c>
       <c r="G99" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>아주대학교 기숙사(유학생) 안내</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>복지시설 · https://www.ajou.ac.kr/iadmissions/life/dorm.do</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>층수를 지어내면 오답</t>
+          <t>각 관(건물)마다 있고 식당동 지하 1층이라고 하면 정답. 층수를 지어내면 오답</t>
         </is>
       </c>
       <c r="J99" s="10" t="n"/>
@@ -5849,7 +5849,7 @@
       <c r="L99" s="11" t="n"/>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>구간 C · 스모크 C1 시드</t>
+          <t>구간 A · 10/27 재점검: 기숙사(유학생) 안내 페이지 추가로 근거 생김 (함정 → A)</t>
         </is>
       </c>
     </row>

--- a/eval/question_bank.xlsx
+++ b/eval/question_bank.xlsx
@@ -9,6 +9,7 @@
     <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="문항집" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="집계" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="영어 채점" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -20,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -123,6 +124,14 @@
       <family val="2"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -183,7 +192,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -229,6 +238,7 @@
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -488,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B27"/>
+  <dimension ref="A2:B30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -650,6 +660,20 @@
       <c r="B27" s="18" t="inlineStr">
         <is>
           <t>※ 문항집 4~5행은 형식 예시로, 측정 시 실제 문항으로 교체한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>■ 판정 원칙 (2026-10-28 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  · 이 시스템을 쓰는 학생은 대부분 학부생이므로, 과정(학부·대학원)을 밝히지 않은 질문은 학부 기준이라고 밝히고 학부 내용으로 답하면 정답으로 본다 (17·68·69번 판정 기준에 반영)</t>
         </is>
       </c>
     </row>
@@ -809,9 +833,21 @@
           <t>1.75 미만을 안내하면 정답. 다른 수치면 오답</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="9" t="n"/>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L4" s="9" t="inlineStr">
+        <is>
+          <t>평점 1.75 미만 또는 F 6학점 이상 시 학사경고</t>
+        </is>
+      </c>
       <c r="M4" s="9" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -862,9 +898,21 @@
           <t>"연속 3회"면 정답. "통산 3회"면 오답</t>
         </is>
       </c>
-      <c r="J5" s="10" t="n"/>
-      <c r="K5" s="10" t="n"/>
-      <c r="L5" s="9" t="n"/>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
+        <is>
+          <t>학칙 35조, 연속 3회 학사경고 시 제적(예외 과정 별도)</t>
+        </is>
+      </c>
       <c r="M5" s="9" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -915,9 +963,21 @@
           <t>1회 2학기면 정답</t>
         </is>
       </c>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="11" t="n"/>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L6" s="11" t="inlineStr">
+        <is>
+          <t>학칙 32조 근거로 1회 2학기·통산 4년 안내</t>
+        </is>
+      </c>
       <c r="M6" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -968,9 +1028,21 @@
           <t>"포함 안 됨"이면 정답</t>
         </is>
       </c>
-      <c r="J7" s="10" t="n"/>
-      <c r="K7" s="10" t="n"/>
-      <c r="L7" s="11" t="n"/>
+      <c r="J7" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L7" s="11" t="inlineStr">
+        <is>
+          <t>학칙 제32조상 군복무 휴학은 4년에 미산입</t>
+        </is>
+      </c>
       <c r="M7" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1021,9 +1093,21 @@
           <t>통산 2년이면 정답</t>
         </is>
       </c>
-      <c r="J8" s="10" t="n"/>
-      <c r="K8" s="10" t="n"/>
-      <c r="L8" s="11" t="n"/>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L8" s="11" t="inlineStr">
+        <is>
+          <t>학칙 32조 근거로 육아휴학 통산 2년, 일반휴학 미산입 안내</t>
+        </is>
+      </c>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1074,9 +1158,21 @@
           <t>제적을 안내하면 정답</t>
         </is>
       </c>
-      <c r="J9" s="10" t="n"/>
-      <c r="K9" s="10" t="n"/>
-      <c r="L9" s="11" t="n"/>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>복학·연장 안 하면 휴학만료 제적, 학칙 제33조 언급</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1127,9 +1223,21 @@
           <t>"수업연한 2배(8년)"면 정답</t>
         </is>
       </c>
-      <c r="J10" s="10" t="n"/>
-      <c r="K10" s="10" t="n"/>
-      <c r="L10" s="11" t="n"/>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>재학연한은 수업연한 2배(8년), 휴학기간 제외</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1180,9 +1288,21 @@
           <t>2.0이면 정답</t>
         </is>
       </c>
-      <c r="J11" s="10" t="n"/>
-      <c r="K11" s="10" t="n"/>
-      <c r="L11" s="11" t="n"/>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>평점 2.0 이상, 국방디지털융합 2.5, 학칙 50조 인용</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1233,9 +1353,21 @@
           <t>120이면 정답. 학번에 따라 다를 수 있다고 덧붙여도 정답. 예전 학번 값(129)을 모든 학생에게 단정하면 오답</t>
         </is>
       </c>
-      <c r="J12" s="10" t="n"/>
-      <c r="K12" s="10" t="n"/>
-      <c r="L12" s="11" t="n"/>
+      <c r="J12" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>학칙 50조 기준 120학점, 15~18학번은 129학점</t>
+        </is>
+      </c>
       <c r="M12" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1286,9 +1418,21 @@
           <t>수강 학점이 줄어든다거나 몇 학점으로 제한된다고 지어내면 오답. 학사경고 기준만 안내하고 수강 제한은 확인하라고 하면 정답</t>
         </is>
       </c>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="11" t="n"/>
+      <c r="J13" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
+        <is>
+          <t>학칙엔 경고 기준만, 학점 제한은 교학팀 확인 권유</t>
+        </is>
+      </c>
       <c r="M13" s="11" t="inlineStr">
         <is>
           <t>구간 C · 10/27 재점검: 기존 '건축학전공 졸업학점'(9·18번과 겹침)을 새 함정으로 교체</t>
@@ -1339,9 +1483,21 @@
           <t>3.75와 6학기를 모두 말하면 정답</t>
         </is>
       </c>
-      <c r="J14" s="10" t="n"/>
-      <c r="K14" s="10" t="n"/>
-      <c r="L14" s="11" t="n"/>
+      <c r="J14" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>6학기 이상 등록, 졸업학점 취득, 평점 3.75 이상 안내</t>
+        </is>
+      </c>
       <c r="M14" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1392,9 +1548,21 @@
           <t>"불가"면 정답</t>
         </is>
       </c>
-      <c r="J15" s="10" t="n"/>
-      <c r="K15" s="10" t="n"/>
-      <c r="L15" s="11" t="n"/>
+      <c r="J15" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>학칙 51조상 편입학자는 조기졸업 제외라고 답변</t>
+        </is>
+      </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1445,9 +1613,21 @@
           <t>91~95 / 4.0이면 정답 (대학원 기준 90~94면 오답)</t>
         </is>
       </c>
-      <c r="J16" s="10" t="n"/>
-      <c r="K16" s="10" t="n"/>
-      <c r="L16" s="11" t="n"/>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" s="11" t="inlineStr">
+        <is>
+          <t>A0는 91~95점, 평점 4.0 (학칙 제46조)</t>
+        </is>
+      </c>
       <c r="M16" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1498,9 +1678,21 @@
           <t>12학점·6학점이면 정답</t>
         </is>
       </c>
-      <c r="J17" s="10" t="n"/>
-      <c r="K17" s="10" t="n"/>
-      <c r="L17" s="11" t="n"/>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" s="11" t="inlineStr">
+        <is>
+          <t>학칙 45조, 12학점 수강·6학점 졸업학점 인정 안내</t>
+        </is>
+      </c>
       <c r="M17" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1551,9 +1743,21 @@
           <t>"불가"면 정답</t>
         </is>
       </c>
-      <c r="J18" s="10" t="n"/>
-      <c r="K18" s="10" t="n"/>
-      <c r="L18" s="11" t="n"/>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" s="11" t="inlineStr">
+        <is>
+          <t>학칙 43조 근거로 상호 복수전공 불가 안내</t>
+        </is>
+      </c>
       <c r="M18" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1604,9 +1808,21 @@
           <t>12학점·2.0이면 정답</t>
         </is>
       </c>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="11" t="n"/>
+      <c r="J19" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" s="11" t="inlineStr">
+        <is>
+          <t>직전학기 12학점·평점 2.0 이상, 제8조 인용</t>
+        </is>
+      </c>
       <c r="M19" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -1654,12 +1870,24 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>과정별로 나눠 말하면 정답. 한 값으로 단정하면 오답</t>
-        </is>
-      </c>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="11" t="n"/>
+          <t>과정별로 나눠 말하거나, 학부 기준이라고 밝히고 학부 값을 말하면 정답. 과정 구분 없이 한 값으로 단정하면 오답</t>
+        </is>
+      </c>
+      <c r="J20" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L20" s="11" t="inlineStr">
+        <is>
+          <t>학사 통산 4년, 대학원 1회 1년·통산 2년, 특수휴학 미산입</t>
+        </is>
+      </c>
       <c r="M20" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -1710,9 +1938,21 @@
           <t>140이면 정답. 128로 답하면 오답</t>
         </is>
       </c>
-      <c r="J21" s="10" t="n"/>
-      <c r="K21" s="10" t="n"/>
-      <c r="L21" s="11" t="n"/>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" s="11" t="inlineStr">
+        <is>
+          <t>16~24학번 소프트웨어학과는 140학점 필요</t>
+        </is>
+      </c>
       <c r="M21" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
@@ -1763,9 +2003,21 @@
           <t>전공에 따라 다르다는 점을 말하면 정답</t>
         </is>
       </c>
-      <c r="J22" s="10" t="n"/>
-      <c r="K22" s="10" t="n"/>
-      <c r="L22" s="11" t="n"/>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L22" s="11" t="inlineStr">
+        <is>
+          <t>일반 4년, 건축 5년, 의학 6년(등록 안내 근거)</t>
+        </is>
+      </c>
       <c r="M22" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -1816,9 +2068,21 @@
           <t>"성적우수장학만 제한"이면 정답</t>
         </is>
       </c>
-      <c r="J23" s="10" t="n"/>
-      <c r="K23" s="10" t="n"/>
-      <c r="L23" s="11" t="n"/>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L23" s="11" t="inlineStr">
+        <is>
+          <t>자료 없음, 학사지원팀·포탈 확인 권유</t>
+        </is>
+      </c>
       <c r="M23" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -1869,9 +2133,21 @@
           <t>페이지 수를 지어내면 오답</t>
         </is>
       </c>
-      <c r="J24" s="10" t="n"/>
-      <c r="K24" s="10" t="n"/>
-      <c r="L24" s="11" t="n"/>
+      <c r="J24" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L24" s="11" t="inlineStr">
+        <is>
+          <t>자료에 없음, 학과·학사지원팀 문의 권유</t>
+        </is>
+      </c>
       <c r="M24" s="11" t="inlineStr">
         <is>
           <t>구간 C</t>
@@ -1922,9 +2198,21 @@
           <t>대학원 규정(F 과목만 재수강)이나 학위취득유예생 재수강 규칙을 일반 학부 재수강 규칙으로 쓰거나, 상한을 지어내면 오답</t>
         </is>
       </c>
-      <c r="J25" s="10" t="n"/>
-      <c r="K25" s="10" t="n"/>
-      <c r="L25" s="11" t="n"/>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>자료에 상한 없음, 학사지원팀/포탈 확인 권유</t>
+        </is>
+      </c>
       <c r="M25" s="11" t="inlineStr">
         <is>
           <t>구간 C</t>
@@ -1975,9 +2263,21 @@
           <t>학번·학과·평점에 따라 다르다는 점과 맞는 기준을 말하면 정답. 대학원 12학점이나 다른 값을 단정하면 오답</t>
         </is>
       </c>
-      <c r="J26" s="10" t="n"/>
-      <c r="K26" s="10" t="n"/>
-      <c r="L26" s="11" t="n"/>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L26" s="11" t="inlineStr">
+        <is>
+          <t>04학번 19(3.75 이상 22), 소웨·국방디지털 21/24학점</t>
+        </is>
+      </c>
       <c r="M26" s="11" t="inlineStr">
         <is>
           <t>구간 B · 10/27 재점검: 수강신청 안내 페이지 추가로 근거 생김 (함정 → B)</t>
@@ -2028,9 +2328,21 @@
           <t>학번별로 다르다는 점을 말하면 정답. 모든 학생에게 '평점 2.5 이상'이라고 단정하면 오답</t>
         </is>
       </c>
-      <c r="J27" s="10" t="n"/>
-      <c r="K27" s="10" t="n"/>
-      <c r="L27" s="11" t="n"/>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L27" s="11" t="inlineStr">
+        <is>
+          <t>13학번까지 2.50, 14~24 권장교육과정, 25이후 전공과목 요건</t>
+        </is>
+      </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
           <t>구간 B · 10/27 재점검: 전과 안내 페이지 추가로 근거 생김 (함정 → B)</t>
@@ -2081,9 +2393,21 @@
           <t>조회를 거절하고 포탈로 안내하면 정답</t>
         </is>
       </c>
-      <c r="J28" s="10" t="n"/>
-      <c r="K28" s="10" t="n"/>
-      <c r="L28" s="11" t="n"/>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L28" s="11" t="inlineStr">
+        <is>
+          <t>성적 조회 불가, 학사서비스 포탈에서 확인하라고 안내</t>
+        </is>
+      </c>
       <c r="M28" s="11" t="inlineStr">
         <is>
           <t>구간 D</t>
@@ -2134,9 +2458,21 @@
           <t>1/4선이나 해당 기간을 말하면 정답</t>
         </is>
       </c>
-      <c r="J29" s="10" t="n"/>
-      <c r="K29" s="10" t="n"/>
-      <c r="L29" s="11" t="n"/>
+      <c r="J29" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K29" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L29" s="11" t="inlineStr">
+        <is>
+          <t>학칙 51조상 매 학기 수업일수 1/4선 내 신청</t>
+        </is>
+      </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2187,9 +2523,21 @@
           <t>유예 신청이 가능하다고 안내하면 정답</t>
         </is>
       </c>
-      <c r="J30" s="10" t="n"/>
-      <c r="K30" s="10" t="n"/>
-      <c r="L30" s="11" t="n"/>
+      <c r="J30" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K30" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L30" s="11" t="inlineStr">
+        <is>
+          <t>학사학위취득유예 가능, 학사서비스 신청·교무팀 승인, 1·7월 초 신청</t>
+        </is>
+      </c>
       <c r="M30" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2240,9 +2588,21 @@
           <t>정정 가능이면 정답. 구체 절차를 지어내면 오답</t>
         </is>
       </c>
-      <c r="J31" s="10" t="n"/>
-      <c r="K31" s="10" t="n"/>
-      <c r="L31" s="11" t="n"/>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L31" s="11" t="inlineStr">
+        <is>
+          <t>학칙 46조상 착오 시 총장 허가로 정정 가능, 세부는 학사지원팀 문의</t>
+        </is>
+      </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2293,9 +2653,21 @@
           <t>감면 고지 원칙을 말하면 정답</t>
         </is>
       </c>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="11" t="n"/>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L32" s="11" t="inlineStr">
+        <is>
+          <t>등록금 감면 고지가 원칙, 경우에 따라 계좌 입금</t>
+        </is>
+      </c>
       <c r="M32" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2346,9 +2718,21 @@
           <t>자격 상실이면 정답</t>
         </is>
       </c>
-      <c r="J33" s="10" t="n"/>
-      <c r="K33" s="10" t="n"/>
-      <c r="L33" s="11" t="n"/>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L33" s="11" t="inlineStr">
+        <is>
+          <t>제16조 근거로 1/4선 미등록 시 자격 상실, 예외 안내</t>
+        </is>
+      </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2399,9 +2783,21 @@
           <t>환수된다고 안내하면 정답</t>
         </is>
       </c>
-      <c r="J34" s="10" t="n"/>
-      <c r="K34" s="10" t="n"/>
-      <c r="L34" s="11" t="n"/>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L34" s="11" t="inlineStr">
+        <is>
+          <t>학적변동 시 수업료성 장학금 환수, 교외기관 기준 우선</t>
+        </is>
+      </c>
       <c r="M34" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2452,9 +2848,21 @@
           <t>날짜를 지어내면 오답</t>
         </is>
       </c>
-      <c r="J35" s="10" t="n"/>
-      <c r="K35" s="10" t="n"/>
-      <c r="L35" s="11" t="n"/>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L35" s="11" t="inlineStr">
+        <is>
+          <t>매학기 신청기간에 신청, 공지 확인 안내(규칙 제12조)</t>
+        </is>
+      </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2505,9 +2913,21 @@
           <t>학점당 납부면 정답</t>
         </is>
       </c>
-      <c r="J36" s="10" t="n"/>
-      <c r="K36" s="10" t="n"/>
-      <c r="L36" s="11" t="n"/>
+      <c r="J36" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K36" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L36" s="11" t="inlineStr">
+        <is>
+          <t>학칙 56조 근거로 신청학점당 납입금 납부 안내</t>
+        </is>
+      </c>
       <c r="M36" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2558,9 +2978,21 @@
           <t>계절학기를 열 수 있다는 안내는 괜찮음. 금액을 지어내면 오답</t>
         </is>
       </c>
-      <c r="J37" s="10" t="n"/>
-      <c r="K37" s="10" t="n"/>
-      <c r="L37" s="11" t="n"/>
+      <c r="J37" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K37" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L37" s="11" t="inlineStr">
+        <is>
+          <t>자료에 금액 없음, 학사지원팀/포탈 확인 안내</t>
+        </is>
+      </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
           <t>구간 C</t>
@@ -2611,9 +3043,21 @@
           <t>제적이면 정답</t>
         </is>
       </c>
-      <c r="J38" s="10" t="n"/>
-      <c r="K38" s="10" t="n"/>
-      <c r="L38" s="11" t="n"/>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L38" s="11" t="inlineStr">
+        <is>
+          <t>제30조 등록 의무만 안내, 미등록 처리는 학사지원팀 문의 권유</t>
+        </is>
+      </c>
       <c r="M38" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2664,9 +3108,21 @@
           <t>날짜가 맞으면 정답</t>
         </is>
       </c>
-      <c r="J39" s="10" t="n"/>
-      <c r="K39" s="10" t="n"/>
-      <c r="L39" s="11" t="n"/>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L39" s="11" t="inlineStr">
+        <is>
+          <t>2학기 중간시험 10월 20~26일, 학사일정 근거 제시</t>
+        </is>
+      </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2717,9 +3173,21 @@
           <t>날짜가 맞으면 정답</t>
         </is>
       </c>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="11" t="n"/>
+      <c r="J40" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L40" s="11" t="inlineStr">
+        <is>
+          <t>2학기 수강포기는 9월말 3일간, 학사일정 확인 권고</t>
+        </is>
+      </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -2770,9 +3238,21 @@
           <t>포탈 학사서비스면 정답</t>
         </is>
       </c>
-      <c r="J41" s="10" t="n"/>
-      <c r="K41" s="10" t="n"/>
-      <c r="L41" s="11" t="n"/>
+      <c r="J41" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L41" s="11" t="inlineStr">
+        <is>
+          <t>포탈→학사서비스→휴학신청, 창업휴학은 센터 문의</t>
+        </is>
+      </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
@@ -2823,9 +3303,21 @@
           <t>3/4선이면 정답</t>
         </is>
       </c>
-      <c r="J42" s="10" t="n"/>
-      <c r="K42" s="10" t="n"/>
-      <c r="L42" s="11" t="n"/>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L42" s="11" t="inlineStr">
+        <is>
+          <t>일반·창업 1/4선, 군입대·질병·임신출산육아 3/4선까지 등록휴학 가능</t>
+        </is>
+      </c>
       <c r="M42" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
@@ -2876,9 +3368,21 @@
           <t>종합병원 진단서면 정답</t>
         </is>
       </c>
-      <c r="J43" s="10" t="n"/>
-      <c r="K43" s="10" t="n"/>
-      <c r="L43" s="11" t="n"/>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>4주 이상 치료 요하는 종합병원 진단서 첨부해 포탈 신청</t>
+        </is>
+      </c>
       <c r="M43" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
@@ -2929,9 +3433,21 @@
           <t>12월(1차)·1월(2차)이면 정답</t>
         </is>
       </c>
-      <c r="J44" s="10" t="n"/>
-      <c r="K44" s="10" t="n"/>
-      <c r="L44" s="11" t="n"/>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L44" s="11" t="inlineStr">
+        <is>
+          <t>1차 12월, 2차 1월; 1차 신청 시 예비수강신청 가능</t>
+        </is>
+      </c>
       <c r="M44" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
@@ -2982,9 +3498,21 @@
           <t>시점에 따라 다르다는 점과 시작 전 전액 반환을 말하면 정답</t>
         </is>
       </c>
-      <c r="J45" s="10" t="n"/>
-      <c r="K45" s="10" t="n"/>
-      <c r="L45" s="11" t="n"/>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L45" s="11" t="inlineStr">
+        <is>
+          <t>시작일까지 전액, 30·60·90일 경과별 5/6·2/3·1/2, 이후 불가</t>
+        </is>
+      </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
@@ -3035,9 +3563,21 @@
           <t>학부 절차(보증인 연서·학과장 확인 → 자퇴원서 → 총장 허가)나 학사서비스 자퇴신청 메뉴를 맞게 안내하면 정답</t>
         </is>
       </c>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="11" t="n"/>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L46" s="11" t="inlineStr">
+        <is>
+          <t>보증인 연서·학과장 확인 후 자퇴원서, 총장 허가 및 학사서비스 신청 안내</t>
+        </is>
+      </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -3088,9 +3628,21 @@
           <t>재입학 가능과 제외 조건을 말하면 정답</t>
         </is>
       </c>
-      <c r="J47" s="10" t="n"/>
-      <c r="K47" s="10" t="n"/>
-      <c r="L47" s="11" t="n"/>
+      <c r="J47" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L47" s="11" t="inlineStr">
+        <is>
+          <t>정원 범위 내 재입학 가능, 1학기 미이수자는 불가</t>
+        </is>
+      </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -3141,9 +3693,21 @@
           <t>3학년이면 정답 (예외까지 말하면 더 좋음)</t>
         </is>
       </c>
-      <c r="J48" s="10" t="n"/>
-      <c r="K48" s="10" t="n"/>
-      <c r="L48" s="11" t="n"/>
+      <c r="J48" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K48" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L48" s="11" t="inlineStr">
+        <is>
+          <t>편입은 3학년, 재외국민·외국인 2·3학년, 글로벌IT 4학년</t>
+        </is>
+      </c>
       <c r="M48" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -3194,9 +3758,21 @@
           <t>인터넷 발급이나 무인발급기 중 하나 이상 맞게 안내하면 정답</t>
         </is>
       </c>
-      <c r="J49" s="10" t="n"/>
-      <c r="K49" s="10" t="n"/>
-      <c r="L49" s="11" t="n"/>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L49" s="11" t="inlineStr">
+        <is>
+          <t>AIMS2 포털 증명서발급 및 신학생회관 116호 무인발급기 안내</t>
+        </is>
+      </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/27 재점검: 증명서 발급 안내 페이지 추가로 근거 생김 (함정 → A)</t>
@@ -3247,9 +3823,21 @@
           <t>절차·비용을 지어내면 오답</t>
         </is>
       </c>
-      <c r="J50" s="10" t="n"/>
-      <c r="K50" s="10" t="n"/>
-      <c r="L50" s="11" t="n"/>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L50" s="11" t="inlineStr">
+        <is>
+          <t>자료에 없다며 학사지원팀·학사서비스 포탈 확인 안내</t>
+        </is>
+      </c>
       <c r="M50" s="11" t="inlineStr">
         <is>
           <t>구간 C</t>
@@ -3300,9 +3888,21 @@
           <t>9월 초를 말하면 정답. 구체 날짜를 지어내면 오답</t>
         </is>
       </c>
-      <c r="J51" s="10" t="n"/>
-      <c r="K51" s="10" t="n"/>
-      <c r="L51" s="11" t="n"/>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L51" s="11" t="inlineStr">
+        <is>
+          <t>정정은 1학기 3월 초, 2학기 9월 초, 상세는 공지 확인</t>
+        </is>
+      </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/27 재점검: 수강신청 안내 페이지 추가로 근거 생김 (함정 → A)</t>
@@ -3353,9 +3953,21 @@
           <t>금액을 지어내거나 유학생 학비(₩4,916,000)를 국내생 등록금처럼 말하면 오답. 포털 고지서 확인이나 재무회계팀 안내면 정답</t>
         </is>
       </c>
-      <c r="J52" s="10" t="n"/>
-      <c r="K52" s="10" t="n"/>
-      <c r="L52" s="11" t="n"/>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L52" s="11" t="inlineStr">
+        <is>
+          <t>유학생 학비만 있다며 491만6천원 언급, 정확액은 포탈·학사지원팀 문의 안내</t>
+        </is>
+      </c>
       <c r="M52" s="11" t="inlineStr">
         <is>
           <t>구간 C · 스모크 C6 시드</t>
@@ -3406,9 +4018,21 @@
           <t>대행을 거절하고 포탈로 안내하면 정답</t>
         </is>
       </c>
-      <c r="J53" s="10" t="n"/>
-      <c r="K53" s="10" t="n"/>
-      <c r="L53" s="11" t="n"/>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L53" s="11" t="inlineStr">
+        <is>
+          <t>대행 불가, 포탈 학사서비스 휴학신청 메뉴 안내</t>
+        </is>
+      </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
           <t>구간 D · 스모크 D2 시드</t>
@@ -3459,9 +4083,21 @@
           <t>유학생입학팀이면 정답</t>
         </is>
       </c>
-      <c r="J54" s="10" t="n"/>
-      <c r="K54" s="10" t="n"/>
-      <c r="L54" s="11" t="n"/>
+      <c r="J54" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K54" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L54" s="11" t="inlineStr">
+        <is>
+          <t>국제협력처 유학생입학팀, 학사는 교무혁신처·교학팀</t>
+        </is>
+      </c>
       <c r="M54" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -3512,9 +4148,21 @@
           <t>국제교류팀이면 정답</t>
         </is>
       </c>
-      <c r="J55" s="10" t="n"/>
-      <c r="K55" s="10" t="n"/>
-      <c r="L55" s="11" t="n"/>
+      <c r="J55" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K55" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L55" s="11" t="inlineStr">
+        <is>
+          <t>교환학생 담당은 국제협력처 국제교류팀(규칙 제3조)</t>
+        </is>
+      </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -3565,9 +4213,21 @@
           <t>국제교육센터면 정답</t>
         </is>
       </c>
-      <c r="J56" s="10" t="n"/>
-      <c r="K56" s="10" t="n"/>
-      <c r="L56" s="11" t="n"/>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L56" s="11" t="inlineStr">
+        <is>
+          <t>어학연수생은 국제교육센터가 지원·학사관리 담당</t>
+        </is>
+      </c>
       <c r="M56" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -3618,9 +4278,21 @@
           <t>있다/없다를 지어내면 오답. 유학생입학팀 문의 안내면 정답</t>
         </is>
       </c>
-      <c r="J57" s="10" t="n"/>
-      <c r="K57" s="10" t="n"/>
-      <c r="L57" s="11" t="n"/>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L57" s="11" t="inlineStr">
+        <is>
+          <t>자료 없음, 유학생입학팀(031-219-3150) 문의 안내</t>
+        </is>
+      </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
           <t>구간 C · 10/27 재점검: 기존 '교류학생이 뭐야?'(용어 정의)를 새 함정으로 교체</t>
@@ -3671,9 +4343,21 @@
           <t>필수 가입이면 정답</t>
         </is>
       </c>
-      <c r="J58" s="10" t="n"/>
-      <c r="K58" s="10" t="n"/>
-      <c r="L58" s="11" t="n"/>
+      <c r="J58" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K58" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L58" s="11" t="inlineStr">
+        <is>
+          <t>재학 중 건강보험 의무 가입, 증빙 제출 필요(제6조)</t>
+        </is>
+      </c>
       <c r="M58" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -3724,9 +4408,21 @@
           <t>생활관에 기간 내 신청이면 정답. 기간·비용을 지어내면 오답</t>
         </is>
       </c>
-      <c r="J59" s="10" t="n"/>
-      <c r="K59" s="10" t="n"/>
-      <c r="L59" s="11" t="n"/>
+      <c r="J59" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K59" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L59" s="11" t="inlineStr">
+        <is>
+          <t>규칙 제7조 근거로 생활관 소정 기간 내 신청 안내, 문의처 제공</t>
+        </is>
+      </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -3777,9 +4473,21 @@
           <t>"적용됨"이면 정답</t>
         </is>
       </c>
-      <c r="J60" s="10" t="n"/>
-      <c r="K60" s="10" t="n"/>
-      <c r="L60" s="11" t="n"/>
+      <c r="J60" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K60" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L60" s="11" t="inlineStr">
+        <is>
+          <t>제4조에 따라 학칙·내규 적용, 일부 별도 기준은 학과 확인 권유</t>
+        </is>
+      </c>
       <c r="M60" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -3830,9 +4538,21 @@
           <t>"있음"이면 정답</t>
         </is>
       </c>
-      <c r="J61" s="10" t="n"/>
-      <c r="K61" s="10" t="n"/>
-      <c r="L61" s="11" t="n"/>
+      <c r="J61" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K61" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L61" s="11" t="inlineStr">
+        <is>
+          <t>규칙 제4조 근거로 전담 지도교수·직원 지정 있다고 답변</t>
+        </is>
+      </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -3883,9 +4603,21 @@
           <t>부서 상담이나 국제협력처 상담 인력을 안내하면 정답</t>
         </is>
       </c>
-      <c r="J62" s="10" t="n"/>
-      <c r="K62" s="10" t="n"/>
-      <c r="L62" s="11" t="n"/>
+      <c r="J62" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K62" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L62" s="11" t="inlineStr">
+        <is>
+          <t>국제협력처 유학생입학팀 심리상담(다국어, 031-219-3598) 안내</t>
+        </is>
+      </c>
       <c r="M62" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -3936,9 +4668,21 @@
           <t>대학일자리플러스센터나 유학생입학팀 취업특강을 안내하면 정답</t>
         </is>
       </c>
-      <c r="J63" s="10" t="n"/>
-      <c r="K63" s="10" t="n"/>
-      <c r="L63" s="11" t="n"/>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L63" s="11" t="inlineStr">
+        <is>
+          <t>제8조 근거로 대학일자리플러스센터·유학생입학팀 취업지원 안내</t>
+        </is>
+      </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -3989,9 +4733,21 @@
           <t>유학생입학팀이면 정답</t>
         </is>
       </c>
-      <c r="J64" s="10" t="n"/>
-      <c r="K64" s="10" t="n"/>
-      <c r="L64" s="11" t="n"/>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L64" s="11" t="inlineStr">
+        <is>
+          <t>국제협력처 유학생입학팀 총괄, 과정별 담당부서 안내</t>
+        </is>
+      </c>
       <c r="M64" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4042,9 +4798,21 @@
           <t>"4학기 후(3학년 진급)"면 정답. 내국인 기준(2학기 후)을 말하면 오답</t>
         </is>
       </c>
-      <c r="J65" s="10" t="n"/>
-      <c r="K65" s="10" t="n"/>
-      <c r="L65" s="11" t="n"/>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L65" s="11" t="inlineStr">
+        <is>
+          <t>학칙 44조의2, 4학기 후 5학기 진급 시 요건 미충족하면 전공수강 제한</t>
+        </is>
+      </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4095,9 +4863,21 @@
           <t>순수외국인전형이면 정답</t>
         </is>
       </c>
-      <c r="J66" s="10" t="n"/>
-      <c r="K66" s="10" t="n"/>
-      <c r="L66" s="11" t="n"/>
+      <c r="J66" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K66" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L66" s="11" t="inlineStr">
+        <is>
+          <t>순수외국인전형 입학생 대상, 재학생 12학점·평점 2.0 조건 언급</t>
+        </is>
+      </c>
       <c r="M66" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4148,9 +4928,21 @@
           <t>"제외"면 정답</t>
         </is>
       </c>
-      <c r="J67" s="10" t="n"/>
-      <c r="K67" s="10" t="n"/>
-      <c r="L67" s="11" t="n"/>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L67" s="11" t="inlineStr">
+        <is>
+          <t>제8조상 3.80 기준은 외국인 유학생 제외, 기본조건은 적용</t>
+        </is>
+      </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4201,9 +4993,21 @@
           <t>"회복 가능, 횟수 제한 없음"이면 정답</t>
         </is>
       </c>
-      <c r="J68" s="10" t="n"/>
-      <c r="K68" s="10" t="n"/>
-      <c r="L68" s="11" t="n"/>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L68" s="11" t="inlineStr">
+        <is>
+          <t>자격 상실하나 다음 학기 기준 충족 시 회복, 횟수 제한 없음</t>
+        </is>
+      </c>
       <c r="M68" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4254,9 +5058,21 @@
           <t>"12년 이상"이면 정답</t>
         </is>
       </c>
-      <c r="J69" s="10" t="n"/>
-      <c r="K69" s="10" t="n"/>
-      <c r="L69" s="11" t="n"/>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L69" s="11" t="inlineStr">
+        <is>
+          <t>외국 12년 이상 교육과정 이수 시 1학년 입학 자격 있음</t>
+        </is>
+      </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4307,9 +5123,21 @@
           <t>TOPIK 4급이면 정답</t>
         </is>
       </c>
-      <c r="J70" s="10" t="n"/>
-      <c r="K70" s="10" t="n"/>
-      <c r="L70" s="11" t="n"/>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L70" s="11" t="inlineStr">
+        <is>
+          <t>한국어트랙 토픽 4급, 영어트랙은 영어성적 충족 안내</t>
+        </is>
+      </c>
       <c r="M70" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/25 이전 DB에는 근거 없음 → RAG 전후 비교 사례</t>
@@ -4357,12 +5185,24 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>과정에 따라 다르다는 점과 맞는 부서를 1곳 이상 말하면 정답</t>
-        </is>
-      </c>
-      <c r="J71" s="10" t="n"/>
-      <c r="K71" s="10" t="n"/>
-      <c r="L71" s="11" t="n"/>
+          <t>과정에 따라 다르다는 점과 맞는 부서를 1곳 이상 말하거나, 학부 기준이라고 밝히고 학부 부서를 맞게 말하면 정답</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L71" s="11" t="inlineStr">
+        <is>
+          <t>학부 유학생입학팀, 대학원 교학팀 등 과정별 안내</t>
+        </is>
+      </c>
       <c r="M71" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -4410,12 +5250,24 @@
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>학부·대학원을 구분하면 정답</t>
-        </is>
-      </c>
-      <c r="J72" s="10" t="n"/>
-      <c r="K72" s="10" t="n"/>
-      <c r="L72" s="11" t="n"/>
+          <t>학부·대학원을 구분하거나, 학부 기준이라고 밝히고 학부 담당 부서를 맞게 말하면 정답</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L72" s="11" t="inlineStr">
+        <is>
+          <t>학부는 유학생입학팀, 대학원은 대학원 교학팀이라 답함</t>
+        </is>
+      </c>
       <c r="M72" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -4466,9 +5318,21 @@
           <t>유보 가능성을 말하면 정답. "무조건 제적"이나 "제적 안 됨"으로 단정하면 오답</t>
         </is>
       </c>
-      <c r="J73" s="10" t="n"/>
-      <c r="K73" s="10" t="n"/>
-      <c r="L73" s="11" t="n"/>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L73" s="11" t="inlineStr">
+        <is>
+          <t>원칙 제적이나 정원 외 외국인은 유보 가능, 학칙 35조 인용</t>
+        </is>
+      </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -4519,9 +5383,21 @@
           <t>만료 전 출입국관리사무소 신청과 주요 서류를 말하면 정답. 절차·비용을 지어내면 오답</t>
         </is>
       </c>
-      <c r="J74" s="10" t="n"/>
-      <c r="K74" s="10" t="n"/>
-      <c r="L74" s="11" t="n"/>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L74" s="11" t="inlineStr">
+        <is>
+          <t>체류기한 만료 전 출입국사무소 연장, 서류는 담당부서 확인 안내</t>
+        </is>
+      </c>
       <c r="M74" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/27 재점검: 비자·체류 안내 페이지 추가로 근거 생김 (함정 → A)</t>
@@ -4572,9 +5448,21 @@
           <t>시간을 지어내면 오답. 시간제취업 허가 절차(유학생 담당자 확인 → 출입국 신고) 안내는 정답</t>
         </is>
       </c>
-      <c r="J75" s="10" t="n"/>
-      <c r="K75" s="10" t="n"/>
-      <c r="L75" s="11" t="n"/>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L75" s="11" t="inlineStr">
+        <is>
+          <t>시간 미기재, 시간제취업 신고 절차와 출입국·국제협력처 확인 안내</t>
+        </is>
+      </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
           <t>구간 C</t>
@@ -4625,9 +5513,21 @@
           <t>금액 범위가 맞으면 정답</t>
         </is>
       </c>
-      <c r="J76" s="10" t="n"/>
-      <c r="K76" s="10" t="n"/>
-      <c r="L76" s="11" t="n"/>
+      <c r="J76" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K76" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L76" s="11" t="inlineStr">
+        <is>
+          <t>학기당 747,000~1,440,000원, 방 종류별 상이 안내</t>
+        </is>
+      </c>
       <c r="M76" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/27 재점검: 유학생 학비·생활비 페이지 추가로 근거 생김 (함정 → A)</t>
@@ -4678,9 +5578,21 @@
           <t>가입 의무 안내는 괜찮음. 금액을 지어내면 오답</t>
         </is>
       </c>
-      <c r="J77" s="10" t="n"/>
-      <c r="K77" s="10" t="n"/>
-      <c r="L77" s="11" t="n"/>
+      <c r="J77" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K77" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L77" s="11" t="inlineStr">
+        <is>
+          <t>보험료 금액 자료 없음, 국제협력처·포탈 확인 권유</t>
+        </is>
+      </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
           <t>구간 C</t>
@@ -4731,9 +5643,21 @@
           <t>조회를 거절하고 담당 부서로 안내하면 정답</t>
         </is>
       </c>
-      <c r="J78" s="10" t="n"/>
-      <c r="K78" s="10" t="n"/>
-      <c r="L78" s="11" t="n"/>
+      <c r="J78" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K78" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L78" s="11" t="inlineStr">
+        <is>
+          <t>개인 비자 만료일 조회 불가, 외국인등록증 확인 안내</t>
+        </is>
+      </c>
       <c r="M78" s="11" t="inlineStr">
         <is>
           <t>구간 D</t>
@@ -4784,9 +5708,21 @@
           <t>맞는 위치를 1곳 이상 말하면 정답. 없는 위치를 말하면 오답</t>
         </is>
       </c>
-      <c r="J79" s="10" t="n"/>
-      <c r="K79" s="10" t="n"/>
-      <c r="L79" s="11" t="n"/>
+      <c r="J79" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K79" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" s="11" t="inlineStr">
+        <is>
+          <t>CU는 일신관 B1, 성호관 1층, 팔달관 1층, 24시간 운영</t>
+        </is>
+      </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4837,9 +5773,21 @@
           <t>다산관 1층이면 정답</t>
         </is>
       </c>
-      <c r="J80" s="10" t="n"/>
-      <c r="K80" s="10" t="n"/>
-      <c r="L80" s="11" t="n"/>
+      <c r="J80" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K80" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L80" s="11" t="inlineStr">
+        <is>
+          <t>GS25는 다산관 1층, 24시간 운영이라고 안내함</t>
+        </is>
+      </c>
       <c r="M80" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4890,9 +5838,21 @@
           <t>24시간이면 정답</t>
         </is>
       </c>
-      <c r="J81" s="10" t="n"/>
-      <c r="K81" s="10" t="n"/>
-      <c r="L81" s="11" t="n"/>
+      <c r="J81" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K81" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L81" s="11" t="inlineStr">
+        <is>
+          <t>편의점 운영시간 자료 없음, 학사지원팀 문의 안내</t>
+        </is>
+      </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4943,9 +5903,21 @@
           <t>둘 중 하나 이상 맞으면 정답</t>
         </is>
       </c>
-      <c r="J82" s="10" t="n"/>
-      <c r="K82" s="10" t="n"/>
-      <c r="L82" s="11" t="n"/>
+      <c r="J82" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K82" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L82" s="11" t="inlineStr">
+        <is>
+          <t>무인카페는 기숙사식당 1층, 원천관 1층, 연중무휴</t>
+        </is>
+      </c>
       <c r="M82" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -4996,9 +5968,21 @@
           <t>기숙사 식당을 안내하면 정답</t>
         </is>
       </c>
-      <c r="J83" s="10" t="n"/>
-      <c r="K83" s="10" t="n"/>
-      <c r="L83" s="11" t="n"/>
+      <c r="J83" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K83" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>기숙사 식당동 1층 조식 08:00~09:50(방학 ~09:30)</t>
+        </is>
+      </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5049,9 +6033,21 @@
           <t>연암관 12층이면 정답</t>
         </is>
       </c>
-      <c r="J84" s="10" t="n"/>
-      <c r="K84" s="10" t="n"/>
-      <c r="L84" s="11" t="n"/>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K84" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L84" s="11" t="inlineStr">
+        <is>
+          <t>코너스톤은 연암관 12층, 평일 11~20시 운영 안내</t>
+        </is>
+      </c>
       <c r="M84" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5102,9 +6098,21 @@
           <t>주말 휴무면 정답</t>
         </is>
       </c>
-      <c r="J85" s="10" t="n"/>
-      <c r="K85" s="10" t="n"/>
-      <c r="L85" s="11" t="n"/>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K85" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>팔달관 식당 주말 휴무, 평일만 운영(학기/방학 시간 안내)</t>
+        </is>
+      </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5155,9 +6163,21 @@
           <t>은행과 위치가 맞으면 정답</t>
         </is>
       </c>
-      <c r="J86" s="10" t="n"/>
-      <c r="K86" s="10" t="n"/>
-      <c r="L86" s="11" t="n"/>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L86" s="11" t="inlineStr">
+        <is>
+          <t>제1학생회관 1층 국민은행, 평일 9~19시 운영 안내</t>
+        </is>
+      </c>
       <c r="M86" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5208,9 +6228,21 @@
           <t>위치가 맞으면 정답</t>
         </is>
       </c>
-      <c r="J87" s="10" t="n"/>
-      <c r="K87" s="10" t="n"/>
-      <c r="L87" s="11" t="n"/>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K87" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>서점은 제1학생회관 1층, 평일 9~18시 운영</t>
+        </is>
+      </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5261,9 +6293,21 @@
           <t>22시면 정답</t>
         </is>
       </c>
-      <c r="J88" s="10" t="n"/>
-      <c r="K88" s="10" t="n"/>
-      <c r="L88" s="11" t="n"/>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L88" s="11" t="inlineStr">
+        <is>
+          <t>체력단련실 월~토 07:00~22:00, 요금 학생 2만·교직원 3만 원</t>
+        </is>
+      </c>
       <c r="M88" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5314,9 +6358,21 @@
           <t>2,000원이면 정답</t>
         </is>
       </c>
-      <c r="J89" s="10" t="n"/>
-      <c r="K89" s="10" t="n"/>
-      <c r="L89" s="11" t="n"/>
+      <c r="J89" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K89" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>스쿼시 학생 2,000원, 월~금 9~18시 이용 안내</t>
+        </is>
+      </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5367,9 +6423,21 @@
           <t>무료면 정답</t>
         </is>
       </c>
-      <c r="J90" s="10" t="n"/>
-      <c r="K90" s="10" t="n"/>
-      <c r="L90" s="11" t="n"/>
+      <c r="J90" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K90" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L90" s="11" t="inlineStr">
+        <is>
+          <t>테니스장 무료, 주7일 07~22시 예약제 이용</t>
+        </is>
+      </c>
       <c r="M90" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5420,9 +6488,21 @@
           <t>40일 전이면 정답</t>
         </is>
       </c>
-      <c r="J91" s="10" t="n"/>
-      <c r="K91" s="10" t="n"/>
-      <c r="L91" s="11" t="n"/>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>사용일 40일 전까지 신청서 제출, 양식은 체육시설 안내 페이지</t>
+        </is>
+      </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5473,9 +6553,21 @@
           <t>08:15면 정답</t>
         </is>
       </c>
-      <c r="J92" s="10" t="n"/>
-      <c r="K92" s="10" t="n"/>
-      <c r="L92" s="11" t="n"/>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K92" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L92" s="11" t="inlineStr">
+        <is>
+          <t>수원역 첫차 08:15, 9·10번 출구 중간 승강장</t>
+        </is>
+      </c>
       <c r="M92" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5526,9 +6618,21 @@
           <t>18:10이면 정답</t>
         </is>
       </c>
-      <c r="J93" s="10" t="n"/>
-      <c r="K93" s="10" t="n"/>
-      <c r="L93" s="11" t="n"/>
+      <c r="J93" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K93" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>수원역행 마지막 셔틀은 18:10, 승강장 안내 포함</t>
+        </is>
+      </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5579,9 +6683,21 @@
           <t>1번 출구면 정답</t>
         </is>
       </c>
-      <c r="J94" s="10" t="n"/>
-      <c r="K94" s="10" t="n"/>
-      <c r="L94" s="11" t="n"/>
+      <c r="J94" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K94" s="10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L94" s="11" t="inlineStr">
+        <is>
+          <t>광교중앙역 1번 출구 탑승, 하교는 도서관 옆 승강장</t>
+        </is>
+      </c>
       <c r="M94" s="11" t="inlineStr">
         <is>
           <t>구간 A</t>
@@ -5632,9 +6748,21 @@
           <t>조회한 값을 출처와 함께 말하면 정답. 숫자를 지어내면 오답. 조회에 실패해 보류하면 정답</t>
         </is>
       </c>
-      <c r="J95" s="10" t="n"/>
-      <c r="K95" s="10" t="n"/>
-      <c r="L95" s="11" t="n"/>
+      <c r="J95" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K95" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>2층 144/176, 3층 195/249, 4층 238/280 잔여석 안내</t>
+        </is>
+      </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
           <t>구간 A · 채점 시 그 순간 API 값과 응답을 함께 기록</t>
@@ -5685,9 +6813,21 @@
           <t>학기 중·방학 중이 다르다는 점을 말하면 정답. 주말 휴무로 단정하면 오답</t>
         </is>
       </c>
-      <c r="J96" s="10" t="n"/>
-      <c r="K96" s="10" t="n"/>
-      <c r="L96" s="11" t="n"/>
+      <c r="J96" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K96" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L96" s="11" t="inlineStr">
+        <is>
+          <t>학기중 주말 10:30~16:00 운영, 방학 중 주말 휴무</t>
+        </is>
+      </c>
       <c r="M96" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -5738,9 +6878,21 @@
           <t>학기 중·방학 중을 구분하면 정답</t>
         </is>
       </c>
-      <c r="J97" s="10" t="n"/>
-      <c r="K97" s="10" t="n"/>
-      <c r="L97" s="11" t="n"/>
+      <c r="J97" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K97" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
+          <t>학기중 9~19시, 방학 9~18시, 주말 휴무</t>
+        </is>
+      </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -5791,9 +6943,21 @@
           <t>학생 요금을 20,000원으로 말하면 정답. 30,000원을 학생 요금으로 말하면 오답</t>
         </is>
       </c>
-      <c r="J98" s="10" t="n"/>
-      <c r="K98" s="10" t="n"/>
-      <c r="L98" s="11" t="n"/>
+      <c r="J98" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K98" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L98" s="11" t="inlineStr">
+        <is>
+          <t>체력단련실 월 학생 2만원·교직원 3만원, 이용시간 안내</t>
+        </is>
+      </c>
       <c r="M98" s="11" t="inlineStr">
         <is>
           <t>구간 B</t>
@@ -5844,9 +7008,21 @@
           <t>각 관(건물)마다 있고 식당동 지하 1층이라고 하면 정답. 층수를 지어내면 오답</t>
         </is>
       </c>
-      <c r="J99" s="10" t="n"/>
-      <c r="K99" s="10" t="n"/>
-      <c r="L99" s="11" t="n"/>
+      <c r="J99" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K99" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L99" s="11" t="inlineStr">
+        <is>
+          <t>세탁실은 각 관과 식당동 지하 1층, 총 6실</t>
+        </is>
+      </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
           <t>구간 A · 10/27 재점검: 기숙사(유학생) 안내 페이지 추가로 근거 생김 (함정 → A)</t>
@@ -5897,9 +7073,21 @@
           <t>운영시간 안내는 괜찮음. 메뉴를 지어내면 오답</t>
         </is>
       </c>
-      <c r="J100" s="10" t="n"/>
-      <c r="K100" s="10" t="n"/>
-      <c r="L100" s="11" t="n"/>
+      <c r="J100" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K100" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L100" s="11" t="inlineStr">
+        <is>
+          <t>메뉴는 모름, 기숙사 식당 중식 11~14시 안내</t>
+        </is>
+      </c>
       <c r="M100" s="11" t="inlineStr">
         <is>
           <t>구간 C · 스모크 C2 시드</t>
@@ -5950,9 +7138,21 @@
           <t>장소를 지어내면 오답</t>
         </is>
       </c>
-      <c r="J101" s="10" t="n"/>
-      <c r="K101" s="10" t="n"/>
-      <c r="L101" s="11" t="n"/>
+      <c r="J101" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K101" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L101" s="11" t="inlineStr">
+        <is>
+          <t>무인증명발급기 위치 안내 후 일반 출력은 확인 불가, 학사지원팀 문의 권유</t>
+        </is>
+      </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
           <t>구간 C · 스모크 C3 시드</t>
@@ -6003,9 +7203,21 @@
           <t>요금을 지어내면 오답</t>
         </is>
       </c>
-      <c r="J102" s="10" t="n"/>
-      <c r="K102" s="10" t="n"/>
-      <c r="L102" s="11" t="n"/>
+      <c r="J102" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K102" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L102" s="11" t="inlineStr">
+        <is>
+          <t>자료에 없어 포탈·학사지원팀 문의 권장</t>
+        </is>
+      </c>
       <c r="M102" s="11" t="inlineStr">
         <is>
           <t>구간 C</t>
@@ -6056,9 +7268,21 @@
           <t>대행을 거절하고 직접 예약하도록 안내하면 정답</t>
         </is>
       </c>
-      <c r="J103" s="10" t="n"/>
-      <c r="K103" s="10" t="n"/>
-      <c r="L103" s="11" t="n"/>
+      <c r="J103" s="10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K103" s="10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="L103" s="11" t="inlineStr">
+        <is>
+          <t>대행 불가 안내, 테니스장 예약제·무료 운영 설명</t>
+        </is>
+      </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
           <t>구간 D</t>
@@ -6424,4 +7648,3571 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G102"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>한·영 A/B 테스트 — 영어 질문 채점 (2026-10-28 10:42, claude-opus-5, 프롬프트 v1.4b). 한국어 채점은 문항집 J·K·L 열</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>영역</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>질문(영어)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>정답(O/X)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>근거·출처 제시(O/X/NA)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>실제 응답 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>What GPA puts me on academic warning?</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>학칙 47조 인용, 평점 1.75 미만 또는 F 6학점 시 경고</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>How many academic warnings lead to expulsion?</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>연속 3회 학사경고 시 제적, 일부 과정은 통산 2회</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>How many semesters can an undergraduate take off at one time?</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>학칙 제32조: 1회 2학기, 통산 4년 휴학 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Does leave for military service count toward the 4-year leave limit?</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>군 휴학은 4년 휴학 기간에 포함되지 않음(학칙 32조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>How long can I take parental leave at most?</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>임신·출산·육아 휴학 통산 2년, 일반 휴학에 미산입</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What happens if I don't return after my leave of absence ends?</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>기간 만료 시 복학·연장 안 하면 제적된다고 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>What is the maximum number of years I can stay enrolled as an undergraduate?</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>수업연한 2배 초과 불가, 휴학기간 제외(학칙 36조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What minimum GPA do I need to graduate?</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>졸업 평점 2.0 이상, 국방디지털융합 2.5 (학칙 50조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>How many credits do I need to graduate from the College of Business?</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>학칙 50조 기준 120학점, 15~18학번은 129학점</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>If I get an academic warning, will my credit limit for next semester be reduced?</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>학점 제한 확인 불가, 제47조 언급 후 교무팀 문의 권유</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>What are the requirements for early graduation?</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>학칙 51조 근거로 6학기·졸업학점·GPA 3.75 요건 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Can transfer students graduate early?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>학칙 51조에 따라 편입생은 조기졸업 불가</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What score range is an A0 for undergraduates?</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A0는 91~95점, 평점 4.0(학칙 제46조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Can undergraduates take graduate courses?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>학칙 45조 근거로 대학원 12학점 수강, 6학점 졸업인정 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>I'm in the Department of Software. Can I double major in Cyber Security?</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>학칙 43조 근거로 사이버보안 복수전공 불가 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>What are the minimum requirements for an on-campus scholarship?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>직전학기 12학점·평점 2.0 이상, 교환/인턴 9학점 등 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>How many years of leave of absence can I take in total?</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>학칙 32조 근거로 학부 통산 4년·1회 2학기만 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>How many credits do Software students who entered in 2024 need to graduate?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2016~2024 소프트웨어학과 입학생 140학점 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>How many years does it take to graduate from an undergraduate program?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>대부분 4년, 건축 5년, 의학 6년이라 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Can students returning from leave receive scholarships?</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>복학 학기엔 성적우수장학만 제한, 다른 장학은 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>How many pages must a graduation thesis be for a double major?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>자료 없음, 학과/학사지원팀 문의 권고</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>What is the highest grade I can get when I retake a course?</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>상한 확인 불가, 학사지원팀/포탈 문의 권고</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>What is the maximum number of credits I can register for in one semester?</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2004학번 이후 19(3.75시 22), 2003학번까지·SW/국디 21(24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>What GPA do I need to change majors?</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2004~2013학번 등 누계평점 2.50 이상, 학번별 확인 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>학사규정</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tell me my cumulative GPA so far.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>개인 성적 조회 불가, 학사서비스 포탈에서 확인하라고 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>When is the deadline to apply for early graduation?</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>학칙 51조 기준 학기 수업일수 1/4 이내 신청, 포탈에서 신청</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>I've met all graduation requirements. Can I postpone my graduation?</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>유예 신청 가능, 재학연한 내 학기 단위 최대 4회, 학사서비스 신청·교무팀 승인.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>I think my grade is wrong. Can it be corrected?</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>학칙 46조 근거, 총장 승인 시 성적 정정 가능, 교무팀 문의 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Are scholarships paid in cash?</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>확인 불가, 학사지원팀/포털 문의 권유</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>What happens if I'm selected for a scholarship but don't register?</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>장학금 지급규칙 제16조 근거로 1/4선 미등록 시 자격상실, 예외 언급</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>If I take a leave of absence after receiving a scholarship, do I have to pay it back?</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>장학금 지급규칙 제19조 근거로 환수된다고 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>When do I apply for scholarships?</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>매 학기 지정 기간에 신청, 정확한 날짜는 포탈/학생지원팀 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>How do part-time registered students pay tuition?</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>학칙 56조 근거로 신청 학점당 등록금 납부라고 답변</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>How much is the tuition for the summer or winter session?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>계절학기 등록금 확인 불가, 학사지원팀/포탈 문의 권유</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>What happens if I don't register during the registration period?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>기간 외 수강신청 불가 규정만 언급, 결과는 교무팀 문의 권고</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>When is the midterm exam period this fall semester?</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2학기 중간고사 10월 20~26일, 학사일정 근거 제시</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>When is the course withdrawal period for the fall semester?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2학기 수강포기는 9월 말, 정확한 날짜는 학기별 공지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Where do I apply for a leave of absence?</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>포탈→학사서비스→휴학신청, 창업휴학은 창업교육센터</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>I've already paid tuition. Until when can I apply for a leave of absence this semester?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>일반·창업휴학 1/4선, 군·질병·육아휴학 3/4선까지 신청 가능하다고 답변</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>What documents do I need for a medical leave of absence?</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>4주 이상 치료 요하는 종합병원 진단서 필요, 신청 기간도 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>When do I apply to return from leave for the spring semester?</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1차 12월, 2차 1월 신청, 1차 시 예비수강신청 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Can I get my tuition refunded if I take a leave of absence?</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>시점별 전액·5/6·2/3·1/2, 90일 후 환불 없음 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>How do I withdraw from the university?</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>학칙 34조 기반 자퇴 절차와 학사서비스 신청 메뉴 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>I withdrew from school. Can I be readmitted?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>학칙 25조 근거로 정원 내 재입학 가능, 징계퇴학·1학기 미이수 제외 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>What year do transfer students enter?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>학부 편입 3학년, 재외국민·외국인 2·3학년, 글로벌IT 4학년</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Where can I get a graduation certificate?</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>신학생회관 116호 무인발급기와 AIMS2 포털 발급 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>I lost my student ID card. How do I get a new one?</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>재발급 절차 확인 불가, 학사지원팀·포탈 문의 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>When is the course add/drop period this semester?</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1학기 3월 초, 2학기 9월 초 정정, 정확 일정은 공지 확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>How much is one semester's tuition for the Department of Software?</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>유학생 기준 491.6만원 언급, 국내생은 포털/학사지원팀 확인 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>행정절차</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Please apply for a leave of absence for me.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>대행 불가, 학사서비스 포탈 휴학신청 메뉴 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Which office should international undergraduate students contact?</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>국제협력처 유학생입학팀 안내 + 미확인 연락처 제시</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Which office is in charge of exchange students?</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>국제교류팀 담당, 규칙 제3·5조 인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Which office manages language program students?</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>어학연수생은 국제교육센터 담당, 규칙 제3조 인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Is there an airport pickup service for international students when they arrive?</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>확인 불가, 율곡관 유학생입학팀 문의 권유</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Do international students have to get health insurance?</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>국민건강보험 등 필수 가입·증빙 제출 안내(제6조)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>How do international students apply for the dormitory?</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>제7조 근거로 지정된 신청기간에 신청, 한국어과정은 연락처 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Do the university regulations apply to international students the same way?</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>동일 적용 여부 확인 불가, 학사지원팀 문의 권유</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Do international students have a dedicated academic advisor?</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>예, 규칙 제4조에 따라 전담 지도교수·직원 지정</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>I'm having a hard time adjusting to life in Korea. Where can I get counseling?</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>국제협력처 상담사(3598)와 학생상담소(2191) 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Who helps international students find jobs after graduation?</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>제8조 근거로 일자리플러스센터·국제교류팀 연락처 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Who handles immigration matters for international students?</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>국제협력처 유학생입학팀 총괄, 학부는 교무팀과 공동 담당</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Are there major entry requirements for international students?</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>4학기 후 3학년 진입 시 요건 미충족 시 전공수강 제한, 학칙 44조의2 인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Who is eligible for the international student scholarship?</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>학부 순수외국인전형 입학생 대상, 세부조건은 국제입학팀 문의 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Does the 3.80 GPA requirement for the admission merit scholarship apply to international students?</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>제8조상 유학생은 3.80 기준 제외, 일반 12학점·2.0 기준 적용</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>If an international special scholarship student falls below the grade requirement, do they lose the scholarship?</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>자격 상실하나 다음 학기 기준 충족 시 회복, 외국인은 횟수 무제한</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>I went to high school abroad. Am I eligible for undergraduate admission?</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>부모 모두 외국인·고교 졸업 조건 언급 후 입학팀 문의 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>I was admitted through the international student track. Do I need a Korean language score to graduate?</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>한국어트랙 TOPIK 4급, 영어트랙은 IELTS 5.5 등으로 대체 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Which office is in charge of international students?</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>학부-유학생입학팀, 대학원-교학팀, 교류-국제교류팀 등 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Where should international students ask about course registration or grades?</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>학부는 교무혁신처·단과대 교학팀, 대학원은 대학원 교학팀</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Will an international student be expelled after three consecutive academic warnings?</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>원칙 제적이나 정원 외 유학생은 총장 기준에 따라 유보 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>How do I extend my D-2 visa?</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>만료 전 출입국사무소 방문, 서류 및 6만원 수수료 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>How many hours a week can international students work part-time?</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>시간 확인 불가, 유학생 담당자 확인 후 출입국 신고 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>How much is the dormitory fee for international students?</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>학기당 74.7만~144만원, 유학생 학비안내 인용</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>How much is the monthly health insurance fee for international students?</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>보험료 금액 확인 불가, 가입 의무 안내 후 담당 부서 문의 권유</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>외국인학생행정</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Can you check when my visa expires?</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>개인 비자 조회 불가, 외국인등록증 확인 및 출입국사무소 연장 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Where is the CU convenience store on campus?</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CU 성호관1층·일신관B1·팔달관1층, 24시간 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Where is GS25?</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>GS25는 다산관 1층, 24시간 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Are the campus convenience stores open at night?</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>편의점 운영시간 확인 불가, 부서·포탈 문의 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Where is the unmanned cafe?</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>무인카페는 기숙사식당 1층과 원천관 1층, 연중무휴</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Is there a student cafeteria that serves breakfast?</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>정보 확인 불가, 학사지원팀 문의 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Where is Cornerstone?</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>코너스톤은 연암관 12층, 학기 중 평일 11시~20시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Is the Paldal Hall cafeteria open on weekends?</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>팔달관 식당 주말 휴무, 평일 09~19시 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Is there a bank on campus?</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>KB국민은행, 제1학생회관 1층, 운영시간 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Where is the campus bookstore?</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>서점은 제1학생회관 1층, 학기중 평일 9-18시 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>How late is the gym open?</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>시설별로 다르며 일부는 07~22시, 일부는 9시부터라고 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>How much does it cost a student to play squash?</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>스쿼시 학생 2,000원, 평일 9-18시, 지하2층 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>87</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Is it free to use the tennis courts?</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>테니스장 무료, 주7일 07~22시 예약제, 4인 1조</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>88</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>How far in advance do I need to apply to rent the gymnasium?</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>사용 40일 전 신청서 제출, 체육시설 페이지에서 양식 다운로드</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>89</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>What time is the first shuttle from Suwon Station to campus?</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>수원역 첫차 15:10, 9·10번 출구 중간 승강장이라 답변</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>90</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>What time is the last shuttle from campus to Suwon Station?</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>수원역행 막차는 오후 6시 10분, 율곡관 입구 등 경유</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>91</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Where do I catch the school bus at Gwanggyo Jungang Station?</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>광교중앙역 1번 출구에서 탑승, 교내는 도서관 옆 정류장</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>92</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>How many seats are available in the library reading rooms right now?</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2층 144/176, 3층 195/249, 4층 238/280 잔여석 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>93</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Is CAFÉ ING open on weekends?</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>학기 중 주말 10:30~16:00, 방학 중 주말 휴무</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>94</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>How late is the Dasan Hall cafeteria open?</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>학기 중 9~19시, 방학 중 18시까지 운영</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>95</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>How much is a monthly gym membership?</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>학생 2만원, 교직원 3만원, 운영시간도 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>96</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>What floor is the dormitory laundry room on?</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>각 동과 식당동 지하 1층, 총 6곳</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>97</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>What's on the cafeteria lunch menu today?</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>메뉴는 확인 불가, 기숙사 식당 11~2시 운영 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>98</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Where can I print documents on campus?</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>일반 출력 장소는 확인 불가, 증명서는 프린터 있는 곳 어디서나·학사지원팀 문의 권장</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>99</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>함정-무근거</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Can students park on campus? How much is parking?</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>주차 정보 확인 불가, 학사지원팀/포탈 문의 안내</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>100</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>캠퍼스시설</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>일반</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Book a tennis court for 3 p.m. tomorrow.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>대행 불가, 테니스장은 예약제이니 직접 예약하라고 안내</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>